--- a/public/lohc-dashboard/demo/lohc_demo_line6.xlsx
+++ b/public/lohc-dashboard/demo/lohc_demo_line6.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CF11"/>
+  <dimension ref="A1:CF16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -856,7 +856,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>725.726242</v>
+        <v>749.815491</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -865,64 +865,64 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="J2" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="K2" t="n">
-        <v>19.49</v>
+        <v>15</v>
       </c>
       <c r="L2" t="n">
         <v>1500</v>
       </c>
       <c r="M2" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="N2" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="O2" t="n">
         <v>1.034</v>
       </c>
       <c r="P2" t="n">
-        <v>642.22253</v>
+        <v>701.938526</v>
       </c>
       <c r="Q2" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="R2" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="S2" t="n">
         <v>1.027</v>
       </c>
       <c r="T2" t="n">
-        <v>378.413655</v>
+        <v>437.267251</v>
       </c>
       <c r="U2" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="V2" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="W2" t="n">
         <v>1.02</v>
       </c>
       <c r="X2" t="n">
-        <v>206.086648</v>
+        <v>208.488365</v>
       </c>
       <c r="Y2" t="n">
-        <v>261.698013</v>
+        <v>252.744152</v>
       </c>
       <c r="Z2" t="n">
-        <v>9.278775749999999</v>
+        <v>8.96844851</v>
       </c>
       <c r="AA2" t="n">
         <v>1.027</v>
       </c>
       <c r="AB2" t="n">
-        <v>378.413242</v>
+        <v>437.280246</v>
       </c>
       <c r="AC2" t="n">
         <v>70</v>
@@ -934,70 +934,70 @@
         <v>50</v>
       </c>
       <c r="AF2" t="n">
-        <v>475.863171</v>
+        <v>596.361795</v>
       </c>
       <c r="AG2" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="AH2" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="AI2" t="n">
         <v>1.013</v>
       </c>
       <c r="AJ2" t="n">
-        <v>191.474288</v>
+        <v>194.808279</v>
       </c>
       <c r="AK2" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="AL2" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="AM2" t="n">
         <v>1.027</v>
       </c>
       <c r="AN2" t="n">
-        <v>376.632019</v>
+        <v>435.406527</v>
       </c>
       <c r="AO2" t="n">
-        <v>-258041.636</v>
+        <v>-241187.022</v>
       </c>
       <c r="AP2" t="n">
-        <v>-47337.9725</v>
+        <v>-54618.0514</v>
       </c>
       <c r="AQ2" t="n">
         <v>32.9836374</v>
       </c>
       <c r="AR2" t="n">
-        <v>397.988204</v>
+        <v>400.518366</v>
       </c>
       <c r="AS2" t="n">
-        <v>-304948.636</v>
+        <v>-295371.571</v>
       </c>
       <c r="AT2" t="n">
-        <v>95.4646865</v>
+        <v>92.1984121</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.38479993</v>
+        <v>3.27159582</v>
       </c>
       <c r="AV2" t="n">
         <v>1.027</v>
       </c>
       <c r="AW2" t="n">
-        <v>378.413242</v>
+        <v>437.280246</v>
       </c>
       <c r="AX2" t="n">
-        <v>95.4646865</v>
+        <v>92.1984121</v>
       </c>
       <c r="AY2" t="n">
-        <v>3.38479993</v>
+        <v>3.27159582</v>
       </c>
       <c r="AZ2" t="n">
         <v>1.027</v>
       </c>
       <c r="BA2" t="n">
-        <v>371.745105</v>
+        <v>430.265643</v>
       </c>
       <c r="BB2" t="n">
         <v>0.293322241</v>
@@ -1021,37 +1021,37 @@
         <v>3.01631243</v>
       </c>
       <c r="BI2" t="n">
-        <v>267.740366</v>
+        <v>308.535418</v>
       </c>
       <c r="BJ2" t="n">
         <v>0.293322241</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.0119077731</v>
+        <v>0.011947963</v>
       </c>
       <c r="BL2" t="n">
         <v>3.01631243</v>
       </c>
       <c r="BM2" t="n">
-        <v>90.02483340000001</v>
+        <v>95.76341240000001</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.00116507753</v>
+        <v>3.99092759e-05</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.749126192</v>
+        <v>0.749970068</v>
       </c>
       <c r="BP2" t="n">
         <v>0.293322241</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.0119077731</v>
+        <v>0.011947963</v>
       </c>
       <c r="BR2" t="n">
         <v>3.01631243</v>
       </c>
       <c r="BS2" t="n">
-        <v>371.745104</v>
+        <v>430.265666</v>
       </c>
       <c r="BT2" t="n">
         <v>70</v>
@@ -1063,7 +1063,7 @@
         <v>50.07</v>
       </c>
       <c r="BW2" t="n">
-        <v>173.868444</v>
+        <v>179.212825</v>
       </c>
       <c r="BX2" t="n">
         <v>70</v>
@@ -1075,7 +1075,7 @@
         <v>50.05</v>
       </c>
       <c r="CA2" t="n">
-        <v>192.431014</v>
+        <v>195.871276</v>
       </c>
       <c r="CB2" t="n">
         <v>70</v>
@@ -1090,27 +1090,27 @@
         <v>264.0032</v>
       </c>
       <c r="CF2" t="n">
-        <v>12.47</v>
+        <v>12.12</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>26</v>
+        <v>85</v>
       </c>
       <c r="B3" t="n">
-        <v>0.9541649276848414</v>
+        <v>0.900039606477535</v>
       </c>
       <c r="C3" t="n">
-        <v>1.560159829958601</v>
+        <v>2.883545909747892</v>
       </c>
       <c r="D3" t="n">
-        <v>6.693258723721784</v>
+        <v>4.640928735980101</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>2245.36941</v>
+        <v>3245.94494</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -1119,64 +1119,64 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="J3" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="K3" t="n">
-        <v>19.49</v>
+        <v>15</v>
       </c>
       <c r="L3" t="n">
         <v>1500</v>
       </c>
       <c r="M3" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="N3" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="O3" t="n">
         <v>1.034</v>
       </c>
       <c r="P3" t="n">
-        <v>642.22253</v>
+        <v>701.938526</v>
       </c>
       <c r="Q3" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="R3" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="S3" t="n">
         <v>1.027</v>
       </c>
       <c r="T3" t="n">
-        <v>374.7139</v>
+        <v>428.240388</v>
       </c>
       <c r="U3" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="V3" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="W3" t="n">
         <v>1.02</v>
       </c>
       <c r="X3" t="n">
-        <v>205.795927</v>
+        <v>207.590146</v>
       </c>
       <c r="Y3" t="n">
-        <v>340.792122</v>
+        <v>310.46197</v>
       </c>
       <c r="Z3" t="n">
-        <v>12.0831398</v>
+        <v>11.0165247</v>
       </c>
       <c r="AA3" t="n">
         <v>1.027</v>
       </c>
       <c r="AB3" t="n">
-        <v>374.71572</v>
+        <v>428.265056</v>
       </c>
       <c r="AC3" t="n">
         <v>70</v>
@@ -1188,124 +1188,124 @@
         <v>50</v>
       </c>
       <c r="AF3" t="n">
-        <v>466.664719</v>
+        <v>581.605461</v>
       </c>
       <c r="AG3" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="AH3" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="AI3" t="n">
         <v>1.013</v>
       </c>
       <c r="AJ3" t="n">
-        <v>191.117898</v>
+        <v>194.02343</v>
       </c>
       <c r="AK3" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="AL3" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="AM3" t="n">
         <v>1.027</v>
       </c>
       <c r="AN3" t="n">
-        <v>369.197077</v>
+        <v>420.1293</v>
       </c>
       <c r="AO3" t="n">
-        <v>-258041.636</v>
+        <v>-241187.022</v>
       </c>
       <c r="AP3" t="n">
-        <v>-46790.3847</v>
+        <v>-53712.5059</v>
       </c>
       <c r="AQ3" t="n">
         <v>32.9836374</v>
       </c>
       <c r="AR3" t="n">
-        <v>397.797353</v>
+        <v>400.203346</v>
       </c>
       <c r="AS3" t="n">
-        <v>-304401.239</v>
+        <v>-294466.341</v>
       </c>
       <c r="AT3" t="n">
-        <v>16.3705782</v>
+        <v>34.4805945</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.580435907</v>
+        <v>1.22351965</v>
       </c>
       <c r="AV3" t="n">
         <v>1.027</v>
       </c>
       <c r="AW3" t="n">
-        <v>374.71572</v>
+        <v>428.265056</v>
       </c>
       <c r="AX3" t="n">
-        <v>16.3705782</v>
+        <v>34.4805945</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.580435907</v>
+        <v>1.22351965</v>
       </c>
       <c r="AZ3" t="n">
         <v>1.027</v>
       </c>
       <c r="BA3" t="n">
-        <v>252.588053</v>
+        <v>346.124272</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.68667283</v>
+        <v>1.16949437</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.0171779655</v>
+        <v>0.0119107474</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.56015983</v>
+        <v>2.88354591</v>
       </c>
       <c r="BE3" t="n">
         <v>15</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.68667283</v>
+        <v>1.16949437</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.0171779655</v>
+        <v>0.0119107474</v>
       </c>
       <c r="BH3" t="n">
-        <v>1.56015983</v>
+        <v>2.88354591</v>
       </c>
       <c r="BI3" t="n">
-        <v>116.848967</v>
+        <v>142.813214</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1.68667283</v>
+        <v>1.16949437</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.0346298757</v>
+        <v>0.0468875487</v>
       </c>
       <c r="BL3" t="n">
-        <v>1.56015983</v>
+        <v>2.88354591</v>
       </c>
       <c r="BM3" t="n">
-        <v>154.300391</v>
+        <v>181.58904</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.32805957</v>
+        <v>0.0053705858</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.503955323</v>
+        <v>0.745972061</v>
       </c>
       <c r="BP3" t="n">
-        <v>1.68667283</v>
+        <v>1.16949437</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.0346298757</v>
+        <v>0.0468875487</v>
       </c>
       <c r="BR3" t="n">
-        <v>1.56015983</v>
+        <v>2.88354591</v>
       </c>
       <c r="BS3" t="n">
-        <v>252.587022</v>
+        <v>346.124407</v>
       </c>
       <c r="BT3" t="n">
         <v>70</v>
@@ -1317,7 +1317,7 @@
         <v>50.07</v>
       </c>
       <c r="BW3" t="n">
-        <v>173.457035</v>
+        <v>178.558327</v>
       </c>
       <c r="BX3" t="n">
         <v>70</v>
@@ -1329,7 +1329,7 @@
         <v>50.05</v>
       </c>
       <c r="CA3" t="n">
-        <v>192.08137</v>
+        <v>195.083824</v>
       </c>
       <c r="CB3" t="n">
         <v>70</v>
@@ -1344,27 +1344,27 @@
         <v>264.0032</v>
       </c>
       <c r="CF3" t="n">
-        <v>13.06</v>
+        <v>11.12</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="B4" t="n">
-        <v>0.7657770943359703</v>
+        <v>0.9885671128266984</v>
       </c>
       <c r="C4" t="n">
-        <v>4.733414207087896</v>
+        <v>2.268692255902076</v>
       </c>
       <c r="D4" t="n">
-        <v>12.24400314542359</v>
+        <v>8.050093219425186</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>5648.51313</v>
+        <v>1136.3343</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -1373,64 +1373,64 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="J4" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="K4" t="n">
-        <v>19.49</v>
+        <v>15</v>
       </c>
       <c r="L4" t="n">
         <v>1500</v>
       </c>
       <c r="M4" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="N4" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="O4" t="n">
         <v>1.034</v>
       </c>
       <c r="P4" t="n">
-        <v>642.22253</v>
+        <v>701.938526</v>
       </c>
       <c r="Q4" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="R4" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="S4" t="n">
         <v>1.027</v>
       </c>
       <c r="T4" t="n">
-        <v>366.904263</v>
+        <v>435.835777</v>
       </c>
       <c r="U4" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="V4" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="W4" t="n">
         <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>205.398043</v>
+        <v>208.417911</v>
       </c>
       <c r="Y4" t="n">
-        <v>273.507014</v>
+        <v>340.998875</v>
       </c>
       <c r="Z4" t="n">
-        <v>9.69747619</v>
+        <v>12.1001053</v>
       </c>
       <c r="AA4" t="n">
         <v>1.027</v>
       </c>
       <c r="AB4" t="n">
-        <v>366.903542</v>
+        <v>435.86307</v>
       </c>
       <c r="AC4" t="n">
         <v>70</v>
@@ -1442,124 +1442,124 @@
         <v>50</v>
       </c>
       <c r="AF4" t="n">
-        <v>445.887695</v>
+        <v>594.110998</v>
       </c>
       <c r="AG4" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="AH4" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="AI4" t="n">
         <v>1.013</v>
       </c>
       <c r="AJ4" t="n">
-        <v>190.479718</v>
+        <v>194.768136</v>
       </c>
       <c r="AK4" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="AL4" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="AM4" t="n">
         <v>1.027</v>
       </c>
       <c r="AN4" t="n">
-        <v>352.979364</v>
+        <v>433.022144</v>
       </c>
       <c r="AO4" t="n">
-        <v>-258041.636</v>
+        <v>-241187.022</v>
       </c>
       <c r="AP4" t="n">
-        <v>-45555.0819</v>
+        <v>-54479.633</v>
       </c>
       <c r="AQ4" t="n">
         <v>32.9836374</v>
       </c>
       <c r="AR4" t="n">
-        <v>397.365854</v>
+        <v>400.470192</v>
       </c>
       <c r="AS4" t="n">
-        <v>-303166.368</v>
+        <v>-295233.201</v>
       </c>
       <c r="AT4" t="n">
-        <v>83.6556853</v>
+        <v>3.94368942</v>
       </c>
       <c r="AU4" t="n">
-        <v>2.96609949</v>
+        <v>0.139939046</v>
       </c>
       <c r="AV4" t="n">
         <v>1.027</v>
       </c>
       <c r="AW4" t="n">
-        <v>366.903542</v>
+        <v>435.86307</v>
       </c>
       <c r="AX4" t="n">
-        <v>83.6556853</v>
+        <v>3.94368942</v>
       </c>
       <c r="AY4" t="n">
-        <v>2.96609949</v>
+        <v>0.139939046</v>
       </c>
       <c r="AZ4" t="n">
         <v>1.027</v>
       </c>
       <c r="BA4" t="n">
-        <v>307.12021</v>
+        <v>179.643683</v>
       </c>
       <c r="BB4" t="n">
-        <v>3.08543689</v>
+        <v>2.02858937</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.0314237164</v>
+        <v>0.0206602239</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.73341421</v>
+        <v>2.26869226</v>
       </c>
       <c r="BE4" t="n">
         <v>15</v>
       </c>
       <c r="BF4" t="n">
-        <v>3.08543689</v>
+        <v>2.02858937</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.0314237164</v>
+        <v>0.0206602239</v>
       </c>
       <c r="BH4" t="n">
-        <v>4.73341421</v>
+        <v>2.26869226</v>
       </c>
       <c r="BI4" t="n">
-        <v>103.724203</v>
+        <v>84.4473708</v>
       </c>
       <c r="BJ4" t="n">
-        <v>3.08543689</v>
+        <v>2.02858937</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.07728085780000001</v>
+        <v>0.0221224784</v>
       </c>
       <c r="BL4" t="n">
-        <v>4.73341421</v>
+        <v>2.26869226</v>
       </c>
       <c r="BM4" t="n">
-        <v>231.077581</v>
+        <v>129.08831</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.208822767</v>
+        <v>0.911869157</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.593382925</v>
+        <v>0.0660981324</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.08543689</v>
+        <v>2.02858937</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.07728085780000001</v>
+        <v>0.0221224784</v>
       </c>
       <c r="BR4" t="n">
-        <v>4.73341421</v>
+        <v>2.26869226</v>
       </c>
       <c r="BS4" t="n">
-        <v>304.080174</v>
+        <v>179.64316</v>
       </c>
       <c r="BT4" t="n">
         <v>70</v>
@@ -1571,7 +1571,7 @@
         <v>50.07</v>
       </c>
       <c r="BW4" t="n">
-        <v>172.522481</v>
+        <v>179.112934</v>
       </c>
       <c r="BX4" t="n">
         <v>70</v>
@@ -1583,7 +1583,7 @@
         <v>50.05</v>
       </c>
       <c r="CA4" t="n">
-        <v>191.465864</v>
+        <v>195.834164</v>
       </c>
       <c r="CB4" t="n">
         <v>70</v>
@@ -1598,27 +1598,27 @@
         <v>264.0032</v>
       </c>
       <c r="CF4" t="n">
-        <v>12.85</v>
+        <v>12.64</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="B5" t="n">
-        <v>0.8608475558196444</v>
+        <v>0.7960971611878542</v>
       </c>
       <c r="C5" t="n">
-        <v>4.780671716148315</v>
+        <v>3.4422461338782</v>
       </c>
       <c r="D5" t="n">
-        <v>17.34492963618063</v>
+        <v>11.32367731904402</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>5247.31851</v>
+        <v>7363.32552</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -1627,64 +1627,64 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="J5" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="K5" t="n">
-        <v>19.49</v>
+        <v>15</v>
       </c>
       <c r="L5" t="n">
         <v>1500</v>
       </c>
       <c r="M5" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="N5" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="O5" t="n">
         <v>1.034</v>
       </c>
       <c r="P5" t="n">
-        <v>642.22253</v>
+        <v>701.938526</v>
       </c>
       <c r="Q5" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="R5" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="S5" t="n">
         <v>1.027</v>
       </c>
       <c r="T5" t="n">
-        <v>367.793581</v>
+        <v>414.708951</v>
       </c>
       <c r="U5" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="V5" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="W5" t="n">
         <v>1.02</v>
       </c>
       <c r="X5" t="n">
-        <v>205.427225</v>
+        <v>206.414776</v>
       </c>
       <c r="Y5" t="n">
-        <v>307.462637</v>
+        <v>274.607796</v>
       </c>
       <c r="Z5" t="n">
-        <v>10.9014082</v>
+        <v>9.74426454</v>
       </c>
       <c r="AA5" t="n">
         <v>1.027</v>
       </c>
       <c r="AB5" t="n">
-        <v>367.79388</v>
+        <v>414.704486</v>
       </c>
       <c r="AC5" t="n">
         <v>70</v>
@@ -1696,124 +1696,124 @@
         <v>50</v>
       </c>
       <c r="AF5" t="n">
-        <v>448.351215</v>
+        <v>556.8238229999999</v>
       </c>
       <c r="AG5" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="AH5" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="AI5" t="n">
         <v>1.013</v>
       </c>
       <c r="AJ5" t="n">
-        <v>190.545144</v>
+        <v>192.926005</v>
       </c>
       <c r="AK5" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="AL5" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="AM5" t="n">
         <v>1.027</v>
       </c>
       <c r="AN5" t="n">
-        <v>354.863121</v>
+        <v>396.162482</v>
       </c>
       <c r="AO5" t="n">
-        <v>-258041.636</v>
+        <v>-241187.022</v>
       </c>
       <c r="AP5" t="n">
-        <v>-45701.4933</v>
+        <v>-52201.657</v>
       </c>
       <c r="AQ5" t="n">
         <v>32.9836374</v>
       </c>
       <c r="AR5" t="n">
-        <v>397.417077</v>
+        <v>399.678327</v>
       </c>
       <c r="AS5" t="n">
-        <v>-303312.728</v>
+        <v>-292956.017</v>
       </c>
       <c r="AT5" t="n">
-        <v>49.7000626</v>
+        <v>70.33476810000001</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.76216751</v>
+        <v>2.49577979</v>
       </c>
       <c r="AV5" t="n">
         <v>1.027</v>
       </c>
       <c r="AW5" t="n">
-        <v>367.79388</v>
+        <v>414.704486</v>
       </c>
       <c r="AX5" t="n">
-        <v>49.7000626</v>
+        <v>70.33476810000001</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.76216751</v>
+        <v>2.49577979</v>
       </c>
       <c r="AZ5" t="n">
         <v>1.027</v>
       </c>
       <c r="BA5" t="n">
-        <v>273.949361</v>
+        <v>322.940317</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.37084875</v>
+        <v>2.85351868</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.0445150285</v>
+        <v>0.0290617391</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.78067172</v>
+        <v>3.44224613</v>
       </c>
       <c r="BE5" t="n">
         <v>15</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.37084875</v>
+        <v>2.85351868</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.0445150285</v>
+        <v>0.0290617391</v>
       </c>
       <c r="BH5" t="n">
-        <v>4.78067172</v>
+        <v>3.44224613</v>
       </c>
       <c r="BI5" t="n">
-        <v>77.57330690000001</v>
+        <v>113.182465</v>
       </c>
       <c r="BJ5" t="n">
-        <v>4.37084875</v>
+        <v>2.85351868</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.0723377744</v>
+        <v>0.10048796</v>
       </c>
       <c r="BL5" t="n">
-        <v>4.78067172</v>
+        <v>3.44224613</v>
       </c>
       <c r="BM5" t="n">
-        <v>220.802832</v>
+        <v>240.731354</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.487169811</v>
+        <v>0.0522749054</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.384622642</v>
+        <v>0.710793821</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.37084875</v>
+        <v>2.85351868</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.0723377744</v>
+        <v>0.10048796</v>
       </c>
       <c r="BR5" t="n">
-        <v>4.78067172</v>
+        <v>3.44224613</v>
       </c>
       <c r="BS5" t="n">
-        <v>273.264493</v>
+        <v>319.325061</v>
       </c>
       <c r="BT5" t="n">
         <v>70</v>
@@ -1825,7 +1825,7 @@
         <v>50.07</v>
       </c>
       <c r="BW5" t="n">
-        <v>172.633743</v>
+        <v>177.460725</v>
       </c>
       <c r="BX5" t="n">
         <v>70</v>
@@ -1837,7 +1837,7 @@
         <v>50.05</v>
       </c>
       <c r="CA5" t="n">
-        <v>191.52833</v>
+        <v>193.995653</v>
       </c>
       <c r="CB5" t="n">
         <v>70</v>
@@ -1852,27 +1852,27 @@
         <v>264.0032</v>
       </c>
       <c r="CF5" t="n">
-        <v>11.76</v>
+        <v>10.58</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="B6" t="n">
-        <v>0.7884545107831802</v>
+        <v>0.8200311114740316</v>
       </c>
       <c r="C6" t="n">
-        <v>1.785324435135212</v>
+        <v>3.699914891284651</v>
       </c>
       <c r="D6" t="n">
-        <v>22.96990220098981</v>
+        <v>15.030118095402</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>8374.30018</v>
+        <v>7666.70652</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -1881,64 +1881,64 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="J6" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="K6" t="n">
-        <v>19.49</v>
+        <v>15</v>
       </c>
       <c r="L6" t="n">
         <v>1500</v>
       </c>
       <c r="M6" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="N6" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="O6" t="n">
         <v>1.034</v>
       </c>
       <c r="P6" t="n">
-        <v>642.22253</v>
+        <v>701.938526</v>
       </c>
       <c r="Q6" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="R6" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="S6" t="n">
         <v>1.027</v>
       </c>
       <c r="T6" t="n">
-        <v>361.075002</v>
+        <v>413.770662</v>
       </c>
       <c r="U6" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="V6" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="W6" t="n">
         <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>205.335456</v>
+        <v>206.329272</v>
       </c>
       <c r="Y6" t="n">
-        <v>281.606542</v>
+        <v>282.863635</v>
       </c>
       <c r="Z6" t="n">
-        <v>9.98465337</v>
+        <v>10.0372172</v>
       </c>
       <c r="AA6" t="n">
         <v>1.027</v>
       </c>
       <c r="AB6" t="n">
-        <v>361.07318</v>
+        <v>413.762669</v>
       </c>
       <c r="AC6" t="n">
         <v>70</v>
@@ -1950,124 +1950,124 @@
         <v>50</v>
       </c>
       <c r="AF6" t="n">
-        <v>429.06899</v>
+        <v>554.978255</v>
       </c>
       <c r="AG6" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="AH6" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="AI6" t="n">
         <v>1.013</v>
       </c>
       <c r="AJ6" t="n">
-        <v>190.099766</v>
+        <v>192.838317</v>
       </c>
       <c r="AK6" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="AL6" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="AM6" t="n">
         <v>1.027</v>
       </c>
       <c r="AN6" t="n">
-        <v>340.382697</v>
+        <v>394.450328</v>
       </c>
       <c r="AO6" t="n">
-        <v>-258041.636</v>
+        <v>-241187.022</v>
       </c>
       <c r="AP6" t="n">
-        <v>-44555.2877</v>
+        <v>-52089.6148</v>
       </c>
       <c r="AQ6" t="n">
         <v>32.9836374</v>
       </c>
       <c r="AR6" t="n">
-        <v>397.015341</v>
+        <v>399.639412</v>
       </c>
       <c r="AS6" t="n">
-        <v>-302166.924</v>
+        <v>-292844.013</v>
       </c>
       <c r="AT6" t="n">
-        <v>75.556158</v>
+        <v>62.0789299</v>
       </c>
       <c r="AU6" t="n">
-        <v>2.67892231</v>
+        <v>2.20282717</v>
       </c>
       <c r="AV6" t="n">
         <v>1.027</v>
       </c>
       <c r="AW6" t="n">
-        <v>361.07318</v>
+        <v>413.762669</v>
       </c>
       <c r="AX6" t="n">
-        <v>75.556158</v>
+        <v>62.0789299</v>
       </c>
       <c r="AY6" t="n">
-        <v>2.67892231</v>
+        <v>2.20282717</v>
       </c>
       <c r="AZ6" t="n">
         <v>1.027</v>
       </c>
       <c r="BA6" t="n">
-        <v>262.340034</v>
+        <v>305.263606</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.78831799</v>
+        <v>3.78752605</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.0589512828</v>
+        <v>0.0385741626</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.78532444</v>
+        <v>3.69991489</v>
       </c>
       <c r="BE6" t="n">
         <v>15</v>
       </c>
       <c r="BF6" t="n">
-        <v>5.78831799</v>
+        <v>3.78752605</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.0589512828</v>
+        <v>0.0385741626</v>
       </c>
       <c r="BH6" t="n">
-        <v>1.78532444</v>
+        <v>3.69991489</v>
       </c>
       <c r="BI6" t="n">
-        <v>62.4750804</v>
+        <v>91.52420739999999</v>
       </c>
       <c r="BJ6" t="n">
-        <v>5.78831799</v>
+        <v>3.78752605</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.116609202</v>
+        <v>0.103986582</v>
       </c>
       <c r="BL6" t="n">
-        <v>1.78532444</v>
+        <v>3.69991489</v>
       </c>
       <c r="BM6" t="n">
-        <v>216.819768</v>
+        <v>239.70188</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.340727623</v>
+        <v>0.161271026</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.494454283</v>
+        <v>0.62904673</v>
       </c>
       <c r="BP6" t="n">
-        <v>5.78831799</v>
+        <v>3.78752605</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.116609202</v>
+        <v>0.103986582</v>
       </c>
       <c r="BR6" t="n">
-        <v>1.78532444</v>
+        <v>3.69991489</v>
       </c>
       <c r="BS6" t="n">
-        <v>255.976266</v>
+        <v>301.02095</v>
       </c>
       <c r="BT6" t="n">
         <v>70</v>
@@ -2079,7 +2079,7 @@
         <v>50.07</v>
       </c>
       <c r="BW6" t="n">
-        <v>171.758807</v>
+        <v>177.379029</v>
       </c>
       <c r="BX6" t="n">
         <v>70</v>
@@ -2091,7 +2091,7 @@
         <v>50.05</v>
       </c>
       <c r="CA6" t="n">
-        <v>191.111756</v>
+        <v>193.908307</v>
       </c>
       <c r="CB6" t="n">
         <v>70</v>
@@ -2106,27 +2106,27 @@
         <v>264.0032</v>
       </c>
       <c r="CF6" t="n">
-        <v>13.18</v>
+        <v>11.35</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>97</v>
+        <v>55</v>
       </c>
       <c r="B7" t="n">
-        <v>0.7998833838777819</v>
+        <v>0.9229665539425764</v>
       </c>
       <c r="C7" t="n">
-        <v>4.159143262124595</v>
+        <v>3.143399747467511</v>
       </c>
       <c r="D7" t="n">
-        <v>28.0902768853589</v>
+        <v>18.56948752193753</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>7909.2672</v>
+        <v>5084.14709</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -2135,64 +2135,64 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="J7" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="K7" t="n">
-        <v>19.49</v>
+        <v>15</v>
       </c>
       <c r="L7" t="n">
         <v>1500</v>
       </c>
       <c r="M7" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="N7" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="O7" t="n">
         <v>1.034</v>
       </c>
       <c r="P7" t="n">
-        <v>642.22253</v>
+        <v>701.938526</v>
       </c>
       <c r="Q7" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="R7" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="S7" t="n">
         <v>1.027</v>
       </c>
       <c r="T7" t="n">
-        <v>362.04654</v>
+        <v>421.951037</v>
       </c>
       <c r="U7" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="V7" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="W7" t="n">
         <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>205.327047</v>
+        <v>207.071496</v>
       </c>
       <c r="Y7" t="n">
-        <v>285.688509</v>
+        <v>318.37045</v>
       </c>
       <c r="Z7" t="n">
-        <v>10.1293838</v>
+        <v>11.2971515</v>
       </c>
       <c r="AA7" t="n">
         <v>1.027</v>
       </c>
       <c r="AB7" t="n">
-        <v>362.046412</v>
+        <v>421.926137</v>
       </c>
       <c r="AC7" t="n">
         <v>70</v>
@@ -2204,124 +2204,124 @@
         <v>50</v>
       </c>
       <c r="AF7" t="n">
-        <v>431.955072</v>
+        <v>570.502297</v>
       </c>
       <c r="AG7" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="AH7" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="AI7" t="n">
         <v>1.013</v>
       </c>
       <c r="AJ7" t="n">
-        <v>190.154837</v>
+        <v>193.56458</v>
       </c>
       <c r="AK7" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="AL7" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="AM7" t="n">
         <v>1.027</v>
       </c>
       <c r="AN7" t="n">
-        <v>342.512355</v>
+        <v>409.155608</v>
       </c>
       <c r="AO7" t="n">
-        <v>-258041.636</v>
+        <v>-241187.022</v>
       </c>
       <c r="AP7" t="n">
-        <v>-44726.9197</v>
+        <v>-53034.0887</v>
       </c>
       <c r="AQ7" t="n">
         <v>32.9836374</v>
       </c>
       <c r="AR7" t="n">
-        <v>397.07561</v>
+        <v>399.967524</v>
       </c>
       <c r="AS7" t="n">
-        <v>-302338.496</v>
+        <v>-293788.159</v>
       </c>
       <c r="AT7" t="n">
-        <v>71.4741909</v>
+        <v>26.5721144</v>
       </c>
       <c r="AU7" t="n">
-        <v>2.53419191</v>
+        <v>0.942892795</v>
       </c>
       <c r="AV7" t="n">
         <v>1.027</v>
       </c>
       <c r="AW7" t="n">
-        <v>362.046412</v>
+        <v>421.926137</v>
       </c>
       <c r="AX7" t="n">
-        <v>71.4741909</v>
+        <v>26.5721144</v>
       </c>
       <c r="AY7" t="n">
-        <v>2.53419191</v>
+        <v>0.942892795</v>
       </c>
       <c r="AZ7" t="n">
         <v>1.027</v>
       </c>
       <c r="BA7" t="n">
-        <v>263.495568</v>
+        <v>252.930129</v>
       </c>
       <c r="BB7" t="n">
-        <v>7.0786307</v>
+        <v>4.67943214</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.07209250790000001</v>
+        <v>0.0476578046</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.15914326</v>
+        <v>3.14339975</v>
       </c>
       <c r="BE7" t="n">
         <v>15</v>
       </c>
       <c r="BF7" t="n">
-        <v>7.0786307</v>
+        <v>4.67943214</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.07209250790000001</v>
+        <v>0.0476578046</v>
       </c>
       <c r="BH7" t="n">
-        <v>4.15914326</v>
+        <v>3.14339975</v>
       </c>
       <c r="BI7" t="n">
-        <v>56.1722286</v>
+        <v>69.89622540000001</v>
       </c>
       <c r="BJ7" t="n">
-        <v>7.0786307</v>
+        <v>4.67943214</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.107548644</v>
+        <v>0.0722616875</v>
       </c>
       <c r="BL7" t="n">
-        <v>4.15914326</v>
+        <v>3.14339975</v>
       </c>
       <c r="BM7" t="n">
-        <v>226.397179</v>
+        <v>205.795781</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.560432873</v>
+        <v>0.546022542</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.329675345</v>
+        <v>0.340483094</v>
       </c>
       <c r="BP7" t="n">
-        <v>7.0786307</v>
+        <v>4.67943214</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.107548644</v>
+        <v>0.0722616875</v>
       </c>
       <c r="BR7" t="n">
-        <v>4.15914326</v>
+        <v>3.14339975</v>
       </c>
       <c r="BS7" t="n">
-        <v>260.286418</v>
+        <v>252.839535</v>
       </c>
       <c r="BT7" t="n">
         <v>70</v>
@@ -2333,7 +2333,7 @@
         <v>50.07</v>
       </c>
       <c r="BW7" t="n">
-        <v>171.890407</v>
+        <v>178.066375</v>
       </c>
       <c r="BX7" t="n">
         <v>70</v>
@@ -2345,7 +2345,7 @@
         <v>50.05</v>
       </c>
       <c r="CA7" t="n">
-        <v>191.161853</v>
+        <v>194.631413</v>
       </c>
       <c r="CB7" t="n">
         <v>70</v>
@@ -2360,27 +2360,27 @@
         <v>264.0032</v>
       </c>
       <c r="CF7" t="n">
-        <v>11.94</v>
+        <v>10.05</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="B8" t="n">
-        <v>0.7131795539955619</v>
+        <v>0.8256565167998002</v>
       </c>
       <c r="C8" t="n">
-        <v>2.795454956183621</v>
+        <v>1.693504722612562</v>
       </c>
       <c r="D8" t="n">
-        <v>33.75837185953002</v>
+        <v>21.61494904648924</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>10401.3433</v>
+        <v>9376.494570000001</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -2389,64 +2389,64 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="J8" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="K8" t="n">
-        <v>19.49</v>
+        <v>15</v>
       </c>
       <c r="L8" t="n">
         <v>1500</v>
       </c>
       <c r="M8" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="N8" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="O8" t="n">
         <v>1.034</v>
       </c>
       <c r="P8" t="n">
-        <v>642.22253</v>
+        <v>701.938526</v>
       </c>
       <c r="Q8" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="R8" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="S8" t="n">
         <v>1.027</v>
       </c>
       <c r="T8" t="n">
-        <v>356.956258</v>
+        <v>408.646225</v>
       </c>
       <c r="U8" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="V8" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="W8" t="n">
         <v>1.02</v>
       </c>
       <c r="X8" t="n">
-        <v>205.419505</v>
+        <v>205.921773</v>
       </c>
       <c r="Y8" t="n">
-        <v>254.721135</v>
+        <v>284.804076</v>
       </c>
       <c r="Z8" t="n">
-        <v>9.031403259999999</v>
+        <v>10.1060724</v>
       </c>
       <c r="AA8" t="n">
         <v>1.027</v>
       </c>
       <c r="AB8" t="n">
-        <v>356.95944</v>
+        <v>408.6417</v>
       </c>
       <c r="AC8" t="n">
         <v>70</v>
@@ -2458,124 +2458,124 @@
         <v>50</v>
       </c>
       <c r="AF8" t="n">
-        <v>416.444172</v>
+        <v>544.589551</v>
       </c>
       <c r="AG8" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="AH8" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="AI8" t="n">
         <v>1.013</v>
       </c>
       <c r="AJ8" t="n">
-        <v>189.842088</v>
+        <v>192.406645</v>
       </c>
       <c r="AK8" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="AL8" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="AM8" t="n">
         <v>1.027</v>
       </c>
       <c r="AN8" t="n">
-        <v>331.218748</v>
+        <v>384.979495</v>
       </c>
       <c r="AO8" t="n">
-        <v>-258041.636</v>
+        <v>-241187.022</v>
       </c>
       <c r="AP8" t="n">
-        <v>-43803.7827</v>
+        <v>-51460.0993</v>
       </c>
       <c r="AQ8" t="n">
         <v>32.9836374</v>
       </c>
       <c r="AR8" t="n">
-        <v>396.750895</v>
+        <v>399.420798</v>
       </c>
       <c r="AS8" t="n">
-        <v>-301415.684</v>
+        <v>-292214.717</v>
       </c>
       <c r="AT8" t="n">
-        <v>102.441565</v>
+        <v>60.1384882</v>
       </c>
       <c r="AU8" t="n">
-        <v>3.63217243</v>
+        <v>2.13397196</v>
       </c>
       <c r="AV8" t="n">
         <v>1.027</v>
       </c>
       <c r="AW8" t="n">
-        <v>356.95944</v>
+        <v>408.6417</v>
       </c>
       <c r="AX8" t="n">
-        <v>102.441565</v>
+        <v>60.1384882</v>
       </c>
       <c r="AY8" t="n">
-        <v>3.63217243</v>
+        <v>2.13397196</v>
       </c>
       <c r="AZ8" t="n">
         <v>1.027</v>
       </c>
       <c r="BA8" t="n">
-        <v>266.510963</v>
+        <v>271.006384</v>
       </c>
       <c r="BB8" t="n">
-        <v>8.506966609999999</v>
+        <v>5.44687554</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.086639434</v>
+        <v>0.0554738528</v>
       </c>
       <c r="BD8" t="n">
-        <v>2.79545496</v>
+        <v>1.69350472</v>
       </c>
       <c r="BE8" t="n">
         <v>15</v>
       </c>
       <c r="BF8" t="n">
-        <v>8.506966609999999</v>
+        <v>5.44687554</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.086639434</v>
+        <v>0.0554738528</v>
       </c>
       <c r="BH8" t="n">
-        <v>2.79545496</v>
+        <v>1.69350472</v>
       </c>
       <c r="BI8" t="n">
-        <v>49.8430135</v>
+        <v>66.4923361</v>
       </c>
       <c r="BJ8" t="n">
-        <v>8.506966609999999</v>
+        <v>5.44687554</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.141395183</v>
+        <v>0.129644257</v>
       </c>
       <c r="BL8" t="n">
-        <v>2.79545496</v>
+        <v>1.69350472</v>
       </c>
       <c r="BM8" t="n">
-        <v>227.919931</v>
+        <v>222.801354</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.483662287</v>
+        <v>0.237190488</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.387253285</v>
+        <v>0.572107134</v>
       </c>
       <c r="BP8" t="n">
-        <v>8.506966609999999</v>
+        <v>5.44687554</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.141395183</v>
+        <v>0.129644257</v>
       </c>
       <c r="BR8" t="n">
-        <v>2.79545496</v>
+        <v>1.69350472</v>
       </c>
       <c r="BS8" t="n">
-        <v>256.276699</v>
+        <v>264.533511</v>
       </c>
       <c r="BT8" t="n">
         <v>70</v>
@@ -2587,7 +2587,7 @@
         <v>50.07</v>
       </c>
       <c r="BW8" t="n">
-        <v>171.179942</v>
+        <v>176.919203</v>
       </c>
       <c r="BX8" t="n">
         <v>70</v>
@@ -2599,7 +2599,7 @@
         <v>50.05</v>
       </c>
       <c r="CA8" t="n">
-        <v>190.874728</v>
+        <v>193.482171</v>
       </c>
       <c r="CB8" t="n">
         <v>70</v>
@@ -2614,27 +2614,27 @@
         <v>264.0032</v>
       </c>
       <c r="CF8" t="n">
-        <v>13.05</v>
+        <v>11.66</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B9" t="n">
-        <v>0.7193088013713037</v>
+        <v>0.7667825885310414</v>
       </c>
       <c r="C9" t="n">
-        <v>3.76096499535821</v>
+        <v>4.401631015682486</v>
       </c>
       <c r="D9" t="n">
-        <v>39.15582915078864</v>
+        <v>25.10652114682285</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>10656.335</v>
+        <v>9986.60815</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -2643,64 +2643,64 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="J9" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="K9" t="n">
-        <v>19.49</v>
+        <v>15</v>
       </c>
       <c r="L9" t="n">
         <v>1500</v>
       </c>
       <c r="M9" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="N9" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="O9" t="n">
         <v>1.034</v>
       </c>
       <c r="P9" t="n">
-        <v>642.22253</v>
+        <v>701.938526</v>
       </c>
       <c r="Q9" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="R9" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="S9" t="n">
         <v>1.027</v>
       </c>
       <c r="T9" t="n">
-        <v>356.453635</v>
+        <v>406.87139</v>
       </c>
       <c r="U9" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="V9" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="W9" t="n">
         <v>1.02</v>
       </c>
       <c r="X9" t="n">
-        <v>205.44708</v>
+        <v>205.792692</v>
       </c>
       <c r="Y9" t="n">
-        <v>256.910273</v>
+        <v>264.495953</v>
       </c>
       <c r="Z9" t="n">
-        <v>9.10902145</v>
+        <v>9.385452880000001</v>
       </c>
       <c r="AA9" t="n">
         <v>1.027</v>
       </c>
       <c r="AB9" t="n">
-        <v>356.462165</v>
+        <v>406.871008</v>
       </c>
       <c r="AC9" t="n">
         <v>70</v>
@@ -2712,124 +2712,124 @@
         <v>50</v>
       </c>
       <c r="AF9" t="n">
-        <v>414.858866</v>
+        <v>540.870759</v>
       </c>
       <c r="AG9" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="AH9" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="AI9" t="n">
         <v>1.013</v>
       </c>
       <c r="AJ9" t="n">
-        <v>189.82113</v>
+        <v>192.261404</v>
       </c>
       <c r="AK9" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="AL9" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="AM9" t="n">
         <v>1.027</v>
       </c>
       <c r="AN9" t="n">
-        <v>330.085156</v>
+        <v>381.65315</v>
       </c>
       <c r="AO9" t="n">
-        <v>-258041.636</v>
+        <v>-241187.022</v>
       </c>
       <c r="AP9" t="n">
-        <v>-43709.3034</v>
+        <v>-51235.2264</v>
       </c>
       <c r="AQ9" t="n">
         <v>32.9836374</v>
       </c>
       <c r="AR9" t="n">
-        <v>396.71758</v>
+        <v>399.342714</v>
       </c>
       <c r="AS9" t="n">
-        <v>-301321.238</v>
+        <v>-291989.922</v>
       </c>
       <c r="AT9" t="n">
-        <v>100.252426</v>
+        <v>80.446612</v>
       </c>
       <c r="AU9" t="n">
-        <v>3.55455424</v>
+        <v>2.85459145</v>
       </c>
       <c r="AV9" t="n">
         <v>1.027</v>
       </c>
       <c r="AW9" t="n">
-        <v>356.462165</v>
+        <v>406.871008</v>
       </c>
       <c r="AX9" t="n">
-        <v>100.252426</v>
+        <v>80.446612</v>
       </c>
       <c r="AY9" t="n">
-        <v>3.55455424</v>
+        <v>2.85459145</v>
       </c>
       <c r="AZ9" t="n">
         <v>1.027</v>
       </c>
       <c r="BA9" t="n">
-        <v>261.713371</v>
+        <v>297.613926</v>
       </c>
       <c r="BB9" t="n">
-        <v>9.867102969999999</v>
+        <v>6.32673691</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.10049178</v>
+        <v>0.064434825</v>
       </c>
       <c r="BD9" t="n">
-        <v>3.760965</v>
+        <v>4.40163102</v>
       </c>
       <c r="BE9" t="n">
         <v>15</v>
       </c>
       <c r="BF9" t="n">
-        <v>9.867102969999999</v>
+        <v>6.32673691</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.10049178</v>
+        <v>0.064434825</v>
       </c>
       <c r="BH9" t="n">
-        <v>3.760965</v>
+        <v>4.40163102</v>
       </c>
       <c r="BI9" t="n">
-        <v>45.341471</v>
+        <v>65.22346450000001</v>
       </c>
       <c r="BJ9" t="n">
-        <v>9.867102969999999</v>
+        <v>6.32673691</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.144141887</v>
+        <v>0.131991512</v>
       </c>
       <c r="BL9" t="n">
-        <v>3.760965</v>
+        <v>4.40163102</v>
       </c>
       <c r="BM9" t="n">
-        <v>228.194328</v>
+        <v>249.437947</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.5962301840000001</v>
+        <v>0.317565337</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.302827362</v>
+        <v>0.511825997</v>
       </c>
       <c r="BP9" t="n">
-        <v>9.867102969999999</v>
+        <v>6.32673691</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.144141887</v>
+        <v>0.131991512</v>
       </c>
       <c r="BR9" t="n">
-        <v>3.760965</v>
+        <v>4.40163102</v>
       </c>
       <c r="BS9" t="n">
-        <v>252.971168</v>
+        <v>289.036264</v>
       </c>
       <c r="BT9" t="n">
         <v>70</v>
@@ -2841,7 +2841,7 @@
         <v>50.07</v>
       </c>
       <c r="BW9" t="n">
-        <v>171.10685</v>
+        <v>176.7546</v>
       </c>
       <c r="BX9" t="n">
         <v>70</v>
@@ -2853,7 +2853,7 @@
         <v>50.05</v>
       </c>
       <c r="CA9" t="n">
-        <v>190.856943</v>
+        <v>193.339514</v>
       </c>
       <c r="CB9" t="n">
         <v>70</v>
@@ -2868,27 +2868,27 @@
         <v>264.0032</v>
       </c>
       <c r="CF9" t="n">
-        <v>15.08</v>
+        <v>11.69</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>71</v>
+        <v>32</v>
       </c>
       <c r="B10" t="n">
-        <v>0.8348466748615784</v>
+        <v>0.9614936781766767</v>
       </c>
       <c r="C10" t="n">
-        <v>3.892320185560596</v>
+        <v>3.619863762329289</v>
       </c>
       <c r="D10" t="n">
-        <v>44.58198945490923</v>
+        <v>28.49365188472262</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>9122.458909999999</v>
+        <v>4053.66307</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -2897,64 +2897,64 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="J10" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="K10" t="n">
-        <v>19.49</v>
+        <v>15</v>
       </c>
       <c r="L10" t="n">
         <v>1500</v>
       </c>
       <c r="M10" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="N10" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="O10" t="n">
         <v>1.034</v>
       </c>
       <c r="P10" t="n">
-        <v>642.22253</v>
+        <v>701.938526</v>
       </c>
       <c r="Q10" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="R10" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="S10" t="n">
         <v>1.027</v>
       </c>
       <c r="T10" t="n">
-        <v>359.557253</v>
+        <v>425.45226</v>
       </c>
       <c r="U10" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="V10" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="W10" t="n">
         <v>1.02</v>
       </c>
       <c r="X10" t="n">
-        <v>205.304719</v>
+        <v>207.409528</v>
       </c>
       <c r="Y10" t="n">
-        <v>298.176092</v>
+        <v>331.660095</v>
       </c>
       <c r="Z10" t="n">
-        <v>10.5721441</v>
+        <v>11.7687252</v>
       </c>
       <c r="AA10" t="n">
         <v>1.027</v>
       </c>
       <c r="AB10" t="n">
-        <v>359.584599</v>
+        <v>425.469811</v>
       </c>
       <c r="AC10" t="n">
         <v>70</v>
@@ -2966,124 +2966,124 @@
         <v>50</v>
       </c>
       <c r="AF10" t="n">
-        <v>424.490871</v>
+        <v>576.768698</v>
       </c>
       <c r="AG10" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="AH10" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="AI10" t="n">
         <v>1.013</v>
       </c>
       <c r="AJ10" t="n">
-        <v>189.946359</v>
+        <v>193.878364</v>
       </c>
       <c r="AK10" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="AL10" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="AM10" t="n">
         <v>1.027</v>
       </c>
       <c r="AN10" t="n">
-        <v>337.032211</v>
+        <v>415.299936</v>
       </c>
       <c r="AO10" t="n">
-        <v>-258041.636</v>
+        <v>-241187.022</v>
       </c>
       <c r="AP10" t="n">
-        <v>-44282.9264</v>
+        <v>-53416.6685</v>
       </c>
       <c r="AQ10" t="n">
         <v>32.9836374</v>
       </c>
       <c r="AR10" t="n">
-        <v>396.919608</v>
+        <v>400.100494</v>
       </c>
       <c r="AS10" t="n">
-        <v>-301894.659</v>
+        <v>-294170.606</v>
       </c>
       <c r="AT10" t="n">
-        <v>58.9866075</v>
+        <v>13.2824694</v>
       </c>
       <c r="AU10" t="n">
-        <v>2.09143163</v>
+        <v>0.471319086</v>
       </c>
       <c r="AV10" t="n">
         <v>1.027</v>
       </c>
       <c r="AW10" t="n">
-        <v>359.584599</v>
+        <v>425.469811</v>
       </c>
       <c r="AX10" t="n">
-        <v>58.9866075</v>
+        <v>13.2824694</v>
       </c>
       <c r="AY10" t="n">
-        <v>2.09143163</v>
+        <v>0.471319086</v>
       </c>
       <c r="AZ10" t="n">
         <v>1.027</v>
       </c>
       <c r="BA10" t="n">
-        <v>221.127309</v>
+        <v>152.941275</v>
       </c>
       <c r="BB10" t="n">
-        <v>11.2344724</v>
+        <v>7.18027949</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.114417791</v>
+        <v>0.0731277528</v>
       </c>
       <c r="BD10" t="n">
-        <v>3.89232019</v>
+        <v>3.61986376</v>
       </c>
       <c r="BE10" t="n">
         <v>15</v>
       </c>
       <c r="BF10" t="n">
-        <v>11.2344724</v>
+        <v>7.18027949</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.114417791</v>
+        <v>0.0731277528</v>
       </c>
       <c r="BH10" t="n">
-        <v>3.89232019</v>
+        <v>3.61986376</v>
       </c>
       <c r="BI10" t="n">
-        <v>38.3222122</v>
+        <v>39.8712695</v>
       </c>
       <c r="BJ10" t="n">
-        <v>11.2344724</v>
+        <v>7.18027949</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.132507739</v>
+        <v>0.0745538297</v>
       </c>
       <c r="BL10" t="n">
-        <v>3.89232019</v>
+        <v>3.61986376</v>
       </c>
       <c r="BM10" t="n">
-        <v>198.962291</v>
+        <v>152.404225</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.817973421</v>
+        <v>0.9744957990000001</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.136519934</v>
+        <v>0.0191281507</v>
       </c>
       <c r="BP10" t="n">
-        <v>11.2344724</v>
+        <v>7.18027949</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.132507739</v>
+        <v>0.0745538297</v>
       </c>
       <c r="BR10" t="n">
-        <v>3.89232019</v>
+        <v>3.61986376</v>
       </c>
       <c r="BS10" t="n">
-        <v>219.129144</v>
+        <v>152.940873</v>
       </c>
       <c r="BT10" t="n">
         <v>70</v>
@@ -3095,7 +3095,7 @@
         <v>50.07</v>
       </c>
       <c r="BW10" t="n">
-        <v>171.54952</v>
+        <v>178.343976</v>
       </c>
       <c r="BX10" t="n">
         <v>70</v>
@@ -3107,7 +3107,7 @@
         <v>50.05</v>
       </c>
       <c r="CA10" t="n">
-        <v>190.962498</v>
+        <v>194.945496</v>
       </c>
       <c r="CB10" t="n">
         <v>70</v>
@@ -3122,27 +3122,27 @@
         <v>264.0032</v>
       </c>
       <c r="CF10" t="n">
-        <v>12.42</v>
+        <v>10.52</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>56</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7016361300551812</v>
+        <v>0.7477543997268066</v>
       </c>
       <c r="C11" t="n">
-        <v>2.115971753415195</v>
+        <v>1.109321912848855</v>
       </c>
       <c r="D11" t="n">
-        <v>49.73031837929862</v>
+        <v>32.28281868130522</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>12703.8296</v>
+        <v>13032.6546</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -3151,64 +3151,64 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="J11" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="K11" t="n">
-        <v>19.49</v>
+        <v>15</v>
       </c>
       <c r="L11" t="n">
         <v>1500</v>
       </c>
       <c r="M11" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="N11" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="O11" t="n">
         <v>1.034</v>
       </c>
       <c r="P11" t="n">
-        <v>642.22253</v>
+        <v>701.938526</v>
       </c>
       <c r="Q11" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="R11" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="S11" t="n">
         <v>1.027</v>
       </c>
       <c r="T11" t="n">
-        <v>352.465126</v>
+        <v>398.372832</v>
       </c>
       <c r="U11" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="V11" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="W11" t="n">
         <v>1.02</v>
       </c>
       <c r="X11" t="n">
-        <v>205.831772</v>
+        <v>205.283719</v>
       </c>
       <c r="Y11" t="n">
-        <v>250.598254</v>
+        <v>257.93232</v>
       </c>
       <c r="Z11" t="n">
-        <v>8.885222239999999</v>
+        <v>9.152547</v>
       </c>
       <c r="AA11" t="n">
         <v>1.027</v>
       </c>
       <c r="AB11" t="n">
-        <v>352.467745</v>
+        <v>398.372745</v>
       </c>
       <c r="AC11" t="n">
         <v>70</v>
@@ -3220,124 +3220,124 @@
         <v>50</v>
       </c>
       <c r="AF11" t="n">
-        <v>401.918101</v>
+        <v>522.093763</v>
       </c>
       <c r="AG11" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="AH11" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="AI11" t="n">
         <v>1.013</v>
       </c>
       <c r="AJ11" t="n">
-        <v>189.754821</v>
+        <v>191.603783</v>
       </c>
       <c r="AK11" t="n">
-        <v>357.1627</v>
+        <v>344.942565</v>
       </c>
       <c r="AL11" t="n">
-        <v>12.6635757</v>
+        <v>12.2400443</v>
       </c>
       <c r="AM11" t="n">
         <v>1.027</v>
       </c>
       <c r="AN11" t="n">
-        <v>320.97218</v>
+        <v>365.361475</v>
       </c>
       <c r="AO11" t="n">
-        <v>-258041.636</v>
+        <v>-241187.022</v>
       </c>
       <c r="AP11" t="n">
-        <v>-42936.6967</v>
+        <v>-50103.3819</v>
       </c>
       <c r="AQ11" t="n">
         <v>32.9836374</v>
       </c>
       <c r="AR11" t="n">
-        <v>396.444482</v>
+        <v>398.949688</v>
       </c>
       <c r="AS11" t="n">
-        <v>-300548.904</v>
+        <v>-290858.47</v>
       </c>
       <c r="AT11" t="n">
-        <v>106.564445</v>
+        <v>87.0102442</v>
       </c>
       <c r="AU11" t="n">
-        <v>3.77835345</v>
+        <v>3.08749733</v>
       </c>
       <c r="AV11" t="n">
         <v>1.027</v>
       </c>
       <c r="AW11" t="n">
-        <v>352.467745</v>
+        <v>398.372745</v>
       </c>
       <c r="AX11" t="n">
-        <v>106.564445</v>
+        <v>87.0102442</v>
       </c>
       <c r="AY11" t="n">
-        <v>3.77835345</v>
+        <v>3.08749733</v>
       </c>
       <c r="AZ11" t="n">
         <v>1.027</v>
       </c>
       <c r="BA11" t="n">
-        <v>245.948639</v>
+        <v>265.900979</v>
       </c>
       <c r="BB11" t="n">
-        <v>12.5318294</v>
+        <v>8.13513346</v>
       </c>
       <c r="BC11" t="n">
-        <v>0.127630759</v>
+        <v>0.0828524892</v>
       </c>
       <c r="BD11" t="n">
-        <v>2.11597175</v>
+        <v>1.10932191</v>
       </c>
       <c r="BE11" t="n">
         <v>15</v>
       </c>
       <c r="BF11" t="n">
-        <v>12.5318294</v>
+        <v>8.13513346</v>
       </c>
       <c r="BG11" t="n">
-        <v>0.127630759</v>
+        <v>0.0828524892</v>
       </c>
       <c r="BH11" t="n">
-        <v>2.11597175</v>
+        <v>1.10932191</v>
       </c>
       <c r="BI11" t="n">
-        <v>37.557957</v>
+        <v>49.9682919</v>
       </c>
       <c r="BJ11" t="n">
-        <v>12.5318294</v>
+        <v>8.13513346</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.177515509</v>
+        <v>0.18089224</v>
       </c>
       <c r="BL11" t="n">
-        <v>2.11597175</v>
+        <v>1.10932191</v>
       </c>
       <c r="BM11" t="n">
-        <v>213.528135</v>
+        <v>219.533286</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.625311614</v>
+        <v>0.277361661</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.28101629</v>
+        <v>0.541978754</v>
       </c>
       <c r="BP11" t="n">
-        <v>12.5318294</v>
+        <v>8.13513346</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.177515509</v>
+        <v>0.18089224</v>
       </c>
       <c r="BR11" t="n">
-        <v>2.11597175</v>
+        <v>1.10932191</v>
       </c>
       <c r="BS11" t="n">
-        <v>232.339464</v>
+        <v>247.802589</v>
       </c>
       <c r="BT11" t="n">
         <v>70</v>
@@ -3349,7 +3349,7 @@
         <v>50.07</v>
       </c>
       <c r="BW11" t="n">
-        <v>170.506276</v>
+        <v>175.923175</v>
       </c>
       <c r="BX11" t="n">
         <v>70</v>
@@ -3361,7 +3361,7 @@
         <v>50.05</v>
       </c>
       <c r="CA11" t="n">
-        <v>190.822254</v>
+        <v>192.699962</v>
       </c>
       <c r="CB11" t="n">
         <v>70</v>
@@ -3376,7 +3376,1277 @@
         <v>264.0032</v>
       </c>
       <c r="CF11" t="n">
-        <v>13.33</v>
+        <v>11.87</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>12</v>
+      </c>
+      <c r="B12" t="n">
+        <v>0.8171186329389361</v>
+      </c>
+      <c r="C12" t="n">
+        <v>2.756639589113146</v>
+      </c>
+      <c r="D12" t="n">
+        <v>36.17683269579527</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>10562.1738</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>344.942565</v>
+      </c>
+      <c r="J12" t="n">
+        <v>12.2400443</v>
+      </c>
+      <c r="K12" t="n">
+        <v>15</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1500</v>
+      </c>
+      <c r="M12" t="n">
+        <v>344.942565</v>
+      </c>
+      <c r="N12" t="n">
+        <v>12.2400443</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.034</v>
+      </c>
+      <c r="P12" t="n">
+        <v>701.938526</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>344.942565</v>
+      </c>
+      <c r="R12" t="n">
+        <v>12.2400443</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.027</v>
+      </c>
+      <c r="T12" t="n">
+        <v>405.221744</v>
+      </c>
+      <c r="U12" t="n">
+        <v>344.942565</v>
+      </c>
+      <c r="V12" t="n">
+        <v>12.2400443</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X12" t="n">
+        <v>205.678254</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>281.858997</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>10.0015683</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.027</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>405.220873</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>70</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>3.88559045</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>537.342626</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>344.942565</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>12.2400443</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1.013</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>192.127867</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>344.942565</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>12.2400443</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1.027</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>378.533782</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>-241187.022</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>-51022.1056</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>32.9836374</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>399.268712</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>-291776.875</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>63.0835678</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>2.23847604</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>1.027</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>405.220873</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>63.0835678</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>2.23847604</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1.027</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>257.101953</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>9.11640849</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0.0928463115</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>2.75663959</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>15</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>9.11640849</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>0.0928463115</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>2.75663959</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>47.2594775</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>9.11640849</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>0.144259392</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>2.75663959</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>224.869137</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>0.5248089339999999</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>0.3563933</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>9.11640849</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>0.144259392</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>2.75663959</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>251.27365</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>70</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>3.88559045</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>50.07</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>176.598426</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>70</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>3.88559045</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>50.05</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>193.208684</v>
+      </c>
+      <c r="CB12" t="n">
+        <v>70</v>
+      </c>
+      <c r="CC12" t="n">
+        <v>3.88559045</v>
+      </c>
+      <c r="CD12" t="n">
+        <v>50.05</v>
+      </c>
+      <c r="CE12" t="n">
+        <v>264.0032</v>
+      </c>
+      <c r="CF12" t="n">
+        <v>12.09</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>28</v>
+      </c>
+      <c r="B13" t="n">
+        <v>0.7066759520451179</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3.23727561658341</v>
+      </c>
+      <c r="D13" t="n">
+        <v>39.42978619580537</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>13206.6655</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>344.942565</v>
+      </c>
+      <c r="J13" t="n">
+        <v>12.2400443</v>
+      </c>
+      <c r="K13" t="n">
+        <v>15</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1500</v>
+      </c>
+      <c r="M13" t="n">
+        <v>344.942565</v>
+      </c>
+      <c r="N13" t="n">
+        <v>12.2400443</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.034</v>
+      </c>
+      <c r="P13" t="n">
+        <v>701.938526</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>344.942565</v>
+      </c>
+      <c r="R13" t="n">
+        <v>12.2400443</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.027</v>
+      </c>
+      <c r="T13" t="n">
+        <v>397.904563</v>
+      </c>
+      <c r="U13" t="n">
+        <v>344.942565</v>
+      </c>
+      <c r="V13" t="n">
+        <v>12.2400443</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X13" t="n">
+        <v>205.263785</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>243.762615</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>8.649744979999999</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.027</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>397.904406</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>70</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>3.88559045</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>521.012188</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>344.942565</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>12.2400443</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>1.013</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>191.572106</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>344.942565</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>12.2400443</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.027</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>364.446621</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>-241187.022</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>-50038.3583</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>32.9836374</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>398.927107</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>-290793.469</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>101.179949</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>3.59029935</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>1.027</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>397.904406</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>101.179949</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>3.59029935</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>1.027</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>282.689631</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>9.936138980000001</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>0.101194879</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>3.23727562</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>15</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>9.936138980000001</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>0.101194879</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>3.23727562</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>46.8617572</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>9.936138980000001</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>0.175523459</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>3.23727562</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>241.01378</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>0.435375911</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>0.423468067</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>9.936138980000001</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>0.175523459</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>3.23727562</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>266.306188</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>70</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>3.88559045</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>50.07</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>175.875257</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>70</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>3.88559045</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>50.05</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>192.66945</v>
+      </c>
+      <c r="CB13" t="n">
+        <v>70</v>
+      </c>
+      <c r="CC13" t="n">
+        <v>3.88559045</v>
+      </c>
+      <c r="CD13" t="n">
+        <v>50.05</v>
+      </c>
+      <c r="CE13" t="n">
+        <v>264.0032</v>
+      </c>
+      <c r="CF13" t="n">
+        <v>10.48</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>16</v>
+      </c>
+      <c r="B14" t="n">
+        <v>0.7757245051266579</v>
+      </c>
+      <c r="C14" t="n">
+        <v>4.334541068976245</v>
+      </c>
+      <c r="D14" t="n">
+        <v>42.90731211940276</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>11865.26</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>344.942565</v>
+      </c>
+      <c r="J14" t="n">
+        <v>12.2400443</v>
+      </c>
+      <c r="K14" t="n">
+        <v>15</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1500</v>
+      </c>
+      <c r="M14" t="n">
+        <v>344.942565</v>
+      </c>
+      <c r="N14" t="n">
+        <v>12.2400443</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.034</v>
+      </c>
+      <c r="P14" t="n">
+        <v>701.938526</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>344.942565</v>
+      </c>
+      <c r="R14" t="n">
+        <v>12.2400443</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.027</v>
+      </c>
+      <c r="T14" t="n">
+        <v>401.561007</v>
+      </c>
+      <c r="U14" t="n">
+        <v>344.942565</v>
+      </c>
+      <c r="V14" t="n">
+        <v>12.2400443</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X14" t="n">
+        <v>205.449599</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>267.5804</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>9.49490233</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.027</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>401.560991</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>70</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>3.88559045</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>529.323684</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>344.942565</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>12.2400443</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1.013</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>191.84055</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>344.942565</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>12.2400443</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1.027</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>371.541682</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>-241187.022</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>-50538.4975</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>32.9836374</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>399.10079</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>-291293.435</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>77.3621644</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>2.745142</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>1.027</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>401.560991</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>77.3621644</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>2.745142</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>1.027</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>265.968889</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>10.8124608</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>0.110119802</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>4.33454107</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>15</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>10.8124608</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>0.110119802</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>4.33454107</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>43.6274728</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>10.8124608</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>0.158254107</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>4.33454107</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>234.573154</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>0.594455562</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>0.304158328</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>10.8124608</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>0.158254107</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>4.33454107</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>257.688645</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>70</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>3.88559045</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>50.07</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>176.2434</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>70</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>3.88559045</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>50.05</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>192.928893</v>
+      </c>
+      <c r="CB14" t="n">
+        <v>70</v>
+      </c>
+      <c r="CC14" t="n">
+        <v>3.88559045</v>
+      </c>
+      <c r="CD14" t="n">
+        <v>50.05</v>
+      </c>
+      <c r="CE14" t="n">
+        <v>264.0032</v>
+      </c>
+      <c r="CF14" t="n">
+        <v>10.04</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>63</v>
+      </c>
+      <c r="B15" t="n">
+        <v>0.8961660039316968</v>
+      </c>
+      <c r="C15" t="n">
+        <v>2.189764727819622</v>
+      </c>
+      <c r="D15" t="n">
+        <v>46.19332448945885</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>8626.211660000001</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>344.942565</v>
+      </c>
+      <c r="J15" t="n">
+        <v>12.2400443</v>
+      </c>
+      <c r="K15" t="n">
+        <v>15</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1500</v>
+      </c>
+      <c r="M15" t="n">
+        <v>344.942565</v>
+      </c>
+      <c r="N15" t="n">
+        <v>12.2400443</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.034</v>
+      </c>
+      <c r="P15" t="n">
+        <v>701.938526</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>344.942565</v>
+      </c>
+      <c r="R15" t="n">
+        <v>12.2400443</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.027</v>
+      </c>
+      <c r="T15" t="n">
+        <v>410.865863</v>
+      </c>
+      <c r="U15" t="n">
+        <v>344.942565</v>
+      </c>
+      <c r="V15" t="n">
+        <v>12.2400443</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X15" t="n">
+        <v>206.091588</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>309.1258</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>10.9691116</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.027</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>410.858376</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>70</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>3.88559045</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>549.154521</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>344.942565</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>12.2400443</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>1.013</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>192.590789</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>344.942565</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>12.2400443</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1.027</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>389.106739</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>-241187.022</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>-51736.4768</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>32.9836374</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>399.516771</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>-292490.998</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>35.8167649</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>1.27093271</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>1.027</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>410.858376</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>35.8167649</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>1.27093271</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>1.027</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>196.444917</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>11.640522</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0.118553214</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>2.18976473</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>15</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>11.640522</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>0.118553214</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>2.18976473</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>35.0446878</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>11.640522</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>0.133248771</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>2.18976473</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>177.901364</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>0.852951172</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>0.110286621</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>11.640522</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>0.133248771</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>2.18976473</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>195.961508</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>70</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>3.88559045</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>50.07</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>177.121254</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>70</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>3.88559045</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>50.05</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>193.663572</v>
+      </c>
+      <c r="CB15" t="n">
+        <v>70</v>
+      </c>
+      <c r="CC15" t="n">
+        <v>3.88559045</v>
+      </c>
+      <c r="CD15" t="n">
+        <v>50.05</v>
+      </c>
+      <c r="CE15" t="n">
+        <v>264.0032</v>
+      </c>
+      <c r="CF15" t="n">
+        <v>12.97</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>56</v>
+      </c>
+      <c r="B16" t="n">
+        <v>0.7016361300551812</v>
+      </c>
+      <c r="C16" t="n">
+        <v>2.115971753415195</v>
+      </c>
+      <c r="D16" t="n">
+        <v>49.73031837929862</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>14864.9969</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>344.942565</v>
+      </c>
+      <c r="J16" t="n">
+        <v>12.2400443</v>
+      </c>
+      <c r="K16" t="n">
+        <v>15</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1500</v>
+      </c>
+      <c r="M16" t="n">
+        <v>344.942565</v>
+      </c>
+      <c r="N16" t="n">
+        <v>12.2400443</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.034</v>
+      </c>
+      <c r="P16" t="n">
+        <v>701.938526</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>344.942565</v>
+      </c>
+      <c r="R16" t="n">
+        <v>12.2400443</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.027</v>
+      </c>
+      <c r="T16" t="n">
+        <v>393.528424</v>
+      </c>
+      <c r="U16" t="n">
+        <v>344.942565</v>
+      </c>
+      <c r="V16" t="n">
+        <v>12.2400443</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X16" t="n">
+        <v>205.106711</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>242.024166</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>8.588057340000001</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.027</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>393.528705</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>70</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>3.88559045</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>510.654378</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>344.942565</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>12.2400443</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1.013</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>191.275385</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>344.942565</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>12.2400443</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.027</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>355.808772</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>-241187.022</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>-49416.5449</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>32.9836374</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>398.711127</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>-290171.872</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>102.918398</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>3.65198699</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>1.027</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>393.528705</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>102.918398</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>3.65198699</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>1.027</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>265.707443</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>12.5318294</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0.127630759</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>2.11597175</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>15</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>12.5318294</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>0.127630759</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>2.11597175</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>38.9247459</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>12.5318294</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>0.202580645</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>2.11597175</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>226.276188</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>0.506699266</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>0.369975551</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>12.5318294</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>0.202580645</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>2.11597175</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>245.686201</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>70</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>3.88559045</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>50.07</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>175.416124</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>70</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>3.88559045</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>50.05</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>192.386837</v>
+      </c>
+      <c r="CB16" t="n">
+        <v>70</v>
+      </c>
+      <c r="CC16" t="n">
+        <v>3.88559045</v>
+      </c>
+      <c r="CD16" t="n">
+        <v>50.05</v>
+      </c>
+      <c r="CE16" t="n">
+        <v>264.0032</v>
+      </c>
+      <c r="CF16" t="n">
+        <v>10.12</v>
       </c>
     </row>
   </sheetData>
@@ -3424,7 +4694,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -3434,7 +4704,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5">
